--- a/artifacts/任务规格转化.xlsx
+++ b/artifacts/任务规格转化.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格转化" sheetId="1" r:id="R57362edc47644842"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格转化" sheetId="1" r:id="R33340f96cc6245e1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -445,22 +445,6 @@
         <x:v>npm run process返回0，修复库、SQL和三张CSV可读，数据库派生表与报表业务值一致</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" ht="48" customHeight="1">
-      <x:c r="A18" s="5" t="str">
-        <x:v>可验证点</x:v>
-      </x:c>
-      <x:c r="B18" s="5" t="str">
-        <x:v>源表哈希、SQLite完整性、外键、有效主键、排除原因、阶梯费用、credit、封顶减免与报表字段</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="33" customHeight="1">
-      <x:c r="A19" s="5" t="str">
-        <x:v>不适合作为评分点的内容</x:v>
-      </x:c>
-      <x:c r="B19" s="5" t="str">
-        <x:v>CTE拆分、别名、注释、缩进、内部查询顺序、CSV必要引号和LF或CRLF行尾</x:v>
-      </x:c>
-    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/artifacts/任务规格转化.xlsx
+++ b/artifacts/任务规格转化.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格转化" sheetId="1" r:id="R33340f96cc6245e1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格转化" sheetId="1" r:id="R2e6a130079d14049"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -346,15 +346,15 @@
         <x:v>输入来源</x:v>
       </x:c>
       <x:c r="B5" s="5" t="str">
-        <x:v>脱敏API计量演练库、月度计费合同和财务报表字段合同</x:v>
+        <x:v>本次API平台7月计量库、月度计费合同和财务报表合同，租户及账务字段已经脱敏</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="48" customHeight="1">
       <x:c r="A6" s="5" t="str">
-        <x:v>输入获取方式</x:v>
+        <x:v>业务目标</x:v>
       </x:c>
       <x:c r="B6" s="5" t="str">
-        <x:v>解压输入数据包后在input_data目录读取database、rules、starter和tools</x:v>
+        <x:v>按2026年7月计费合同重建租户账单，留下用量资格、重试裁决、额度扣减、阶梯计价、账单调整和月度封顶的追溯结果</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="63" customHeight="1">
@@ -373,12 +373,12 @@
         <x:v>output/api_billing_repaired.db；output/rebuild_api_billing.sql；output/reports/tenant_invoice.csv；output/reports/family_usage.csv；output/reports/exclusion_review.csv</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="33" customHeight="1">
+    <x:row r="9" ht="48" customHeight="1">
       <x:c r="A9" s="5" t="str">
-        <x:v>核心操作链</x:v>
+        <x:v>软件步骤</x:v>
       </x:c>
       <x:c r="B9" s="5" t="str">
-        <x:v>载入合同；筛选用量；裁决重试；扣减额度；阶梯计价；归集credit；应用封顶；整理排除；导出报表</x:v>
+        <x:v>用SQLite载入合同并筛选用量，依次完成重试裁决、额度扣减、阶梯计价、credit归集和月度封顶，再整理排除记录并导出报表</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="48" customHeight="1">
@@ -431,18 +431,18 @@
     </x:row>
     <x:row r="16" ht="33" customHeight="1">
       <x:c r="A16" s="5" t="str">
-        <x:v>输入保护</x:v>
+        <x:v>实现边界</x:v>
       </x:c>
       <x:c r="B16" s="5" t="str">
-        <x:v>五张源表保持不变，正式处理只读本地脱敏材料，不连接外部服务</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" ht="48" customHeight="1">
+        <x:v>保留五张源表，只在输出库建立派生表；全部计算依据随包合同完成，不连接外部服务</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="33" customHeight="1">
       <x:c r="A17" s="5" t="str">
-        <x:v>完成条件</x:v>
+        <x:v>交付要求</x:v>
       </x:c>
       <x:c r="B17" s="5" t="str">
-        <x:v>npm run process返回0，修复库、SQL和三张CSV可读，数据库派生表与报表业务值一致</x:v>
+        <x:v>交付修复库、可执行SQL和三张CSV，数据库派生表与报表采用同一套计费结果</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
